--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91A1FCB-3228-4DBF-AEB8-245C3EC5C642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946D9904-14E2-4E6B-B49B-F35A0ABFF983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="141">
   <si>
     <t>date</t>
   </si>
@@ -448,6 +448,12 @@
   </si>
   <si>
     <t>Debating culture of the EFSPI workshop</t>
+  </si>
+  <si>
+    <t>https://lnkd.in/p/eidq85rx</t>
+  </si>
+  <si>
+    <t>Is an informative prior the same as borrowing?</t>
   </si>
 </sst>
 </file>
@@ -790,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -819,170 +825,170 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46256</v>
+        <v>46275</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46232</v>
+        <v>46256</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46191</v>
+        <v>46232</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46157</v>
+        <v>46191</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>46084</v>
+        <v>46145</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>46030</v>
+        <v>46084</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>45964</v>
+        <v>45989</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -993,768 +999,782 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>45956</v>
+        <v>45959</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>45941</v>
+        <v>45956</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>75</v>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
-      <c r="C22" t="s">
-        <v>87</v>
+      <c r="C22" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>45623</v>
       </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
         <v>80</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>76</v>
+      <c r="C28" t="s">
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
-      <c r="C29" t="s">
-        <v>73</v>
+      <c r="C29" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="D35" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="E40" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B43" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B43" t="s">
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="D43" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D44" t="s">
-        <v>39</v>
-      </c>
-      <c r="E44" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" t="s">
+        <v>39</v>
+      </c>
+      <c r="E45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>45143</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
         <v>35</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A46" s="2">
+    <row r="47" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A47" s="2">
         <v>45119</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
-      </c>
-      <c r="D49" t="s">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>46</v>
+        <v>122</v>
+      </c>
+      <c r="D51" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
-      </c>
-      <c r="D52" t="s">
-        <v>5</v>
+        <v>45</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>11</v>
+        <v>127</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D57" t="s">
-        <v>9</v>
+        <v>128</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="D60" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
-      </c>
-      <c r="D61" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D62" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" t="s">
         <v>22</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D66" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B66" s="2"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B67" s="2"/>
     </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B68" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A36:D56">
-    <sortCondition ref="B36:B56"/>
-    <sortCondition descending="1" ref="A36:A56"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A37:D57">
+    <sortCondition ref="B37:B57"/>
+    <sortCondition descending="1" ref="A37:A57"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D56" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D46" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D47" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D48" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D60" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D43" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D51" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D35" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E28" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D25" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D24" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E22" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E21" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D20" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D19" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D57" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D47" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D49" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D61" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D44" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D52" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D36" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E29" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D26" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D25" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E23" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E22" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D21" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D20" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946D9904-14E2-4E6B-B49B-F35A0ABFF983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C8CDF0-ACF9-4A69-B74A-54028A22449C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="143">
   <si>
     <t>date</t>
   </si>
@@ -454,6 +454,12 @@
   </si>
   <si>
     <t>Is an informative prior the same as borrowing?</t>
+  </si>
+  <si>
+    <t>https://lnkd.in/p/efdeDEsR</t>
+  </si>
+  <si>
+    <t>Is it really worthwhile to run a single-arm trial?</t>
   </si>
 </sst>
 </file>
@@ -796,17 +802,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.453125" customWidth="1"/>
+    <col min="5" max="5" width="99.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -823,189 +829,189 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>46275</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>140</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>46256</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>138</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>46232</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>136</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46191</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>133</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>46157</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>132</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>46148</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>120</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46145</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
         <v>119</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>46084</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
         <v>116</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>46030</v>
       </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>114</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>46001</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>113</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>45992</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
         <v>109</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>45989</v>
       </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>45964</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45964</v>
       </c>
@@ -1013,768 +1019,782 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
         <v>103</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>45959</v>
       </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
         <v>107</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>45956</v>
       </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
         <v>100</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>45941</v>
       </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
         <v>98</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>45927</v>
       </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>97</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>45871</v>
       </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>45868</v>
       </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>45855</v>
       </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>45784</v>
       </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
         <v>87</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>45725</v>
       </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
         <v>85</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>45696</v>
       </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>45686</v>
       </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>45623</v>
       </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
         <v>80</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>45584</v>
       </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>78</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>45568</v>
       </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>45565</v>
       </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
         <v>73</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>45557</v>
       </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
         <v>70</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>45537</v>
       </c>
-      <c r="B32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
         <v>68</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>45533</v>
       </c>
-      <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
         <v>66</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>45509</v>
       </c>
-      <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
         <v>62</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>45504</v>
       </c>
-      <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
         <v>64</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>45490</v>
       </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>45482</v>
       </c>
-      <c r="B37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>58</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>45473</v>
       </c>
-      <c r="B38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
         <v>56</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>45443</v>
       </c>
-      <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
         <v>54</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>45357</v>
       </c>
-      <c r="B40" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
         <v>51</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>52</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E41" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>45352</v>
       </c>
-      <c r="B41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
         <v>50</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>45240</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
         <v>48</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>45212</v>
       </c>
-      <c r="B43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
         <v>44</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
         <v>45211</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
         <v>42</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>45147</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
         <v>38</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>39</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E46" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <v>45143</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>35</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A47" s="2">
+    <row r="48" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
         <v>45119</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="B48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
         <v>45113</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <v>45112</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
         <v>45083</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
         <v>123</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>45082</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
         <v>122</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
         <v>45018</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
         <v>45014</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="B54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
         <v>124</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
         <v>44992</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
         <v>125</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D55" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
         <v>44959</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>126</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D56" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
         <v>44930</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
         <v>127</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
         <v>44897</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
         <v>128</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
         <v>44682</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="B59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
         <v>129</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
         <v>44601</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="B60" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
         <v>130</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D60" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
         <v>44725</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" t="s">
-        <v>31</v>
-      </c>
-      <c r="D60" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="2">
-        <v>44723</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>33</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="D61" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
-      </c>
-      <c r="D62" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D63" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" t="s">
         <v>22</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D67" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B67" s="2"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
     </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B69" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A37:D57">
-    <sortCondition ref="B37:B57"/>
-    <sortCondition descending="1" ref="A37:A57"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:D58">
+    <sortCondition ref="B38:B58"/>
+    <sortCondition descending="1" ref="A38:A58"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D57" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D47" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D49" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D61" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D44" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D52" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D36" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E29" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D26" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D25" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E23" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E22" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D21" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D20" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D58" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D48" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D49" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D50" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D62" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D45" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D53" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D37" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E30" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D27" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D26" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E24" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E23" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D21" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
